--- a/yudao-module-wms/yudao-module-wms-biz/src/main/resources/templates/warehouse-bin-import.xlsx
+++ b/yudao-module-wms/yudao-module-wms-biz/src/main/resources/templates/warehouse-bin-import.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>名称</t>
   </si>
@@ -50,7 +50,23 @@
     <t>高度(mm)</t>
   </si>
   <si>
-    <t>类型(1标准2超长)</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 1标准 2超长</t>
+    </r>
   </si>
   <si>
     <t>层数</t>
@@ -62,22 +78,13 @@
     <t>货架</t>
   </si>
   <si>
-    <t>BZ-01</t>
-  </si>
-  <si>
-    <t>45</t>
+    <t>BZ-0112</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
-    <t>BLP-2</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>12</t>
+    <t>BZ-011</t>
   </si>
 </sst>
 </file>
@@ -90,7 +97,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -259,6 +266,11 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -1329,11 +1341,11 @@
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="2">
+        <v>43</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -1360,18 +1372,39 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:11">
       <c r="A3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="B3" s="2">
+        <v>43</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>50</v>
+      </c>
+      <c r="F3">
+        <v>50</v>
+      </c>
+      <c r="G3">
+        <v>50</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
         <v>2</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
